--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDE75B2-62B2-1F41-A397-2E363F8E7B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319BE1CE-F320-5942-AAAD-A37260D59DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="21500" windowHeight="19940" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="481">
   <si>
     <t>Team</t>
   </si>
@@ -1479,6 +1479,15 @@
   </si>
   <si>
     <t>07/01/2026</t>
+  </si>
+  <si>
+    <t>Robert Wright</t>
+  </si>
+  <si>
+    <t>08/22/2026</t>
+  </si>
+  <si>
+    <t>08/23/2026</t>
   </si>
 </sst>
 </file>
@@ -7507,12 +7516,6 @@
           <cell r="B221">
             <v>220</v>
           </cell>
-          <cell r="E221"/>
-          <cell r="F221"/>
-          <cell r="G221"/>
-          <cell r="H221"/>
-          <cell r="I221"/>
-          <cell r="J221"/>
           <cell r="K221">
             <v>0</v>
           </cell>
@@ -7521,12 +7524,6 @@
           <cell r="B222">
             <v>221</v>
           </cell>
-          <cell r="E222"/>
-          <cell r="F222"/>
-          <cell r="G222"/>
-          <cell r="H222"/>
-          <cell r="I222"/>
-          <cell r="J222"/>
           <cell r="K222">
             <v>0</v>
           </cell>
@@ -7535,12 +7532,6 @@
           <cell r="B223">
             <v>222</v>
           </cell>
-          <cell r="E223"/>
-          <cell r="F223"/>
-          <cell r="G223"/>
-          <cell r="H223"/>
-          <cell r="I223"/>
-          <cell r="J223"/>
           <cell r="K223">
             <v>0</v>
           </cell>
@@ -7549,12 +7540,6 @@
           <cell r="B224">
             <v>223</v>
           </cell>
-          <cell r="E224"/>
-          <cell r="F224"/>
-          <cell r="G224"/>
-          <cell r="H224"/>
-          <cell r="I224"/>
-          <cell r="J224"/>
           <cell r="K224">
             <v>0</v>
           </cell>
@@ -7563,12 +7548,6 @@
           <cell r="B225">
             <v>224</v>
           </cell>
-          <cell r="E225"/>
-          <cell r="F225"/>
-          <cell r="G225"/>
-          <cell r="H225"/>
-          <cell r="I225"/>
-          <cell r="J225"/>
           <cell r="K225">
             <v>0</v>
           </cell>
@@ -7577,12 +7556,6 @@
           <cell r="B226">
             <v>225</v>
           </cell>
-          <cell r="E226"/>
-          <cell r="F226"/>
-          <cell r="G226"/>
-          <cell r="H226"/>
-          <cell r="I226"/>
-          <cell r="J226"/>
           <cell r="K226">
             <v>0</v>
           </cell>
@@ -7591,12 +7564,6 @@
           <cell r="B227">
             <v>226</v>
           </cell>
-          <cell r="E227"/>
-          <cell r="F227"/>
-          <cell r="G227"/>
-          <cell r="H227"/>
-          <cell r="I227"/>
-          <cell r="J227"/>
           <cell r="K227">
             <v>0</v>
           </cell>
@@ -7605,12 +7572,6 @@
           <cell r="B228">
             <v>227</v>
           </cell>
-          <cell r="E228"/>
-          <cell r="F228"/>
-          <cell r="G228"/>
-          <cell r="H228"/>
-          <cell r="I228"/>
-          <cell r="J228"/>
           <cell r="K228">
             <v>0</v>
           </cell>
@@ -7619,12 +7580,6 @@
           <cell r="B229">
             <v>228</v>
           </cell>
-          <cell r="E229"/>
-          <cell r="F229"/>
-          <cell r="G229"/>
-          <cell r="H229"/>
-          <cell r="I229"/>
-          <cell r="J229"/>
           <cell r="K229">
             <v>0</v>
           </cell>
@@ -7633,12 +7588,6 @@
           <cell r="B230">
             <v>229</v>
           </cell>
-          <cell r="E230"/>
-          <cell r="F230"/>
-          <cell r="G230"/>
-          <cell r="H230"/>
-          <cell r="I230"/>
-          <cell r="J230"/>
           <cell r="K230">
             <v>0</v>
           </cell>
@@ -7647,12 +7596,6 @@
           <cell r="B231">
             <v>230</v>
           </cell>
-          <cell r="E231"/>
-          <cell r="F231"/>
-          <cell r="G231"/>
-          <cell r="H231"/>
-          <cell r="I231"/>
-          <cell r="J231"/>
           <cell r="K231">
             <v>0</v>
           </cell>
@@ -7661,12 +7604,6 @@
           <cell r="B232">
             <v>231</v>
           </cell>
-          <cell r="E232"/>
-          <cell r="F232"/>
-          <cell r="G232"/>
-          <cell r="H232"/>
-          <cell r="I232"/>
-          <cell r="J232"/>
           <cell r="K232">
             <v>0</v>
           </cell>
@@ -7675,12 +7612,6 @@
           <cell r="B233">
             <v>232</v>
           </cell>
-          <cell r="E233"/>
-          <cell r="F233"/>
-          <cell r="G233"/>
-          <cell r="H233"/>
-          <cell r="I233"/>
-          <cell r="J233"/>
           <cell r="K233">
             <v>0</v>
           </cell>
@@ -7689,12 +7620,6 @@
           <cell r="B234">
             <v>233</v>
           </cell>
-          <cell r="E234"/>
-          <cell r="F234"/>
-          <cell r="G234"/>
-          <cell r="H234"/>
-          <cell r="I234"/>
-          <cell r="J234"/>
           <cell r="K234">
             <v>0</v>
           </cell>
@@ -7703,12 +7628,6 @@
           <cell r="B235">
             <v>234</v>
           </cell>
-          <cell r="E235"/>
-          <cell r="F235"/>
-          <cell r="G235"/>
-          <cell r="H235"/>
-          <cell r="I235"/>
-          <cell r="J235"/>
           <cell r="K235">
             <v>0</v>
           </cell>
@@ -7717,12 +7636,6 @@
           <cell r="B236">
             <v>235</v>
           </cell>
-          <cell r="E236"/>
-          <cell r="F236"/>
-          <cell r="G236"/>
-          <cell r="H236"/>
-          <cell r="I236"/>
-          <cell r="J236"/>
           <cell r="K236">
             <v>0</v>
           </cell>
@@ -7731,12 +7644,6 @@
           <cell r="B237">
             <v>236</v>
           </cell>
-          <cell r="E237"/>
-          <cell r="F237"/>
-          <cell r="G237"/>
-          <cell r="H237"/>
-          <cell r="I237"/>
-          <cell r="J237"/>
           <cell r="K237">
             <v>0</v>
           </cell>
@@ -7745,12 +7652,6 @@
           <cell r="B238">
             <v>237</v>
           </cell>
-          <cell r="E238"/>
-          <cell r="F238"/>
-          <cell r="G238"/>
-          <cell r="H238"/>
-          <cell r="I238"/>
-          <cell r="J238"/>
           <cell r="K238">
             <v>0</v>
           </cell>
@@ -7759,12 +7660,6 @@
           <cell r="B239">
             <v>238</v>
           </cell>
-          <cell r="E239"/>
-          <cell r="F239"/>
-          <cell r="G239"/>
-          <cell r="H239"/>
-          <cell r="I239"/>
-          <cell r="J239"/>
           <cell r="K239">
             <v>0</v>
           </cell>
@@ -7773,12 +7668,6 @@
           <cell r="B240">
             <v>239</v>
           </cell>
-          <cell r="E240"/>
-          <cell r="F240"/>
-          <cell r="G240"/>
-          <cell r="H240"/>
-          <cell r="I240"/>
-          <cell r="J240"/>
           <cell r="K240">
             <v>0</v>
           </cell>
@@ -7787,12 +7676,6 @@
           <cell r="B241">
             <v>240</v>
           </cell>
-          <cell r="E241"/>
-          <cell r="F241"/>
-          <cell r="G241"/>
-          <cell r="H241"/>
-          <cell r="I241"/>
-          <cell r="J241"/>
           <cell r="K241">
             <v>0</v>
           </cell>
@@ -7801,12 +7684,6 @@
           <cell r="B242">
             <v>241</v>
           </cell>
-          <cell r="E242"/>
-          <cell r="F242"/>
-          <cell r="G242"/>
-          <cell r="H242"/>
-          <cell r="I242"/>
-          <cell r="J242"/>
           <cell r="K242">
             <v>0</v>
           </cell>
@@ -7815,12 +7692,6 @@
           <cell r="B243">
             <v>242</v>
           </cell>
-          <cell r="E243"/>
-          <cell r="F243"/>
-          <cell r="G243"/>
-          <cell r="H243"/>
-          <cell r="I243"/>
-          <cell r="J243"/>
           <cell r="K243">
             <v>0</v>
           </cell>
@@ -7829,12 +7700,6 @@
           <cell r="B244">
             <v>243</v>
           </cell>
-          <cell r="E244"/>
-          <cell r="F244"/>
-          <cell r="G244"/>
-          <cell r="H244"/>
-          <cell r="I244"/>
-          <cell r="J244"/>
           <cell r="K244">
             <v>0</v>
           </cell>
@@ -7843,12 +7708,6 @@
           <cell r="B245">
             <v>244</v>
           </cell>
-          <cell r="E245"/>
-          <cell r="F245"/>
-          <cell r="G245"/>
-          <cell r="H245"/>
-          <cell r="I245"/>
-          <cell r="J245"/>
           <cell r="K245">
             <v>0</v>
           </cell>
@@ -7857,12 +7716,6 @@
           <cell r="B246">
             <v>245</v>
           </cell>
-          <cell r="E246"/>
-          <cell r="F246"/>
-          <cell r="G246"/>
-          <cell r="H246"/>
-          <cell r="I246"/>
-          <cell r="J246"/>
           <cell r="K246">
             <v>0</v>
           </cell>
@@ -7871,12 +7724,6 @@
           <cell r="B247">
             <v>246</v>
           </cell>
-          <cell r="E247"/>
-          <cell r="F247"/>
-          <cell r="G247"/>
-          <cell r="H247"/>
-          <cell r="I247"/>
-          <cell r="J247"/>
           <cell r="K247">
             <v>0</v>
           </cell>
@@ -7885,12 +7732,6 @@
           <cell r="B248">
             <v>247</v>
           </cell>
-          <cell r="E248"/>
-          <cell r="F248"/>
-          <cell r="G248"/>
-          <cell r="H248"/>
-          <cell r="I248"/>
-          <cell r="J248"/>
           <cell r="K248">
             <v>0</v>
           </cell>
@@ -7899,12 +7740,6 @@
           <cell r="B249">
             <v>248</v>
           </cell>
-          <cell r="E249"/>
-          <cell r="F249"/>
-          <cell r="G249"/>
-          <cell r="H249"/>
-          <cell r="I249"/>
-          <cell r="J249"/>
           <cell r="K249">
             <v>0</v>
           </cell>
@@ -7913,12 +7748,6 @@
           <cell r="B250">
             <v>249</v>
           </cell>
-          <cell r="E250"/>
-          <cell r="F250"/>
-          <cell r="G250"/>
-          <cell r="H250"/>
-          <cell r="I250"/>
-          <cell r="J250"/>
           <cell r="K250">
             <v>0</v>
           </cell>
@@ -7927,12 +7756,6 @@
           <cell r="B251">
             <v>250</v>
           </cell>
-          <cell r="E251"/>
-          <cell r="F251"/>
-          <cell r="G251"/>
-          <cell r="H251"/>
-          <cell r="I251"/>
-          <cell r="J251"/>
           <cell r="K251">
             <v>0</v>
           </cell>
@@ -7941,12 +7764,6 @@
           <cell r="B252">
             <v>251</v>
           </cell>
-          <cell r="E252"/>
-          <cell r="F252"/>
-          <cell r="G252"/>
-          <cell r="H252"/>
-          <cell r="I252"/>
-          <cell r="J252"/>
           <cell r="K252">
             <v>0</v>
           </cell>
@@ -7955,12 +7772,6 @@
           <cell r="B253">
             <v>252</v>
           </cell>
-          <cell r="E253"/>
-          <cell r="F253"/>
-          <cell r="G253"/>
-          <cell r="H253"/>
-          <cell r="I253"/>
-          <cell r="J253"/>
           <cell r="K253">
             <v>0</v>
           </cell>
@@ -7969,12 +7780,6 @@
           <cell r="B254">
             <v>253</v>
           </cell>
-          <cell r="E254"/>
-          <cell r="F254"/>
-          <cell r="G254"/>
-          <cell r="H254"/>
-          <cell r="I254"/>
-          <cell r="J254"/>
           <cell r="K254">
             <v>0</v>
           </cell>
@@ -7983,12 +7788,6 @@
           <cell r="B255">
             <v>254</v>
           </cell>
-          <cell r="E255"/>
-          <cell r="F255"/>
-          <cell r="G255"/>
-          <cell r="H255"/>
-          <cell r="I255"/>
-          <cell r="J255"/>
           <cell r="K255">
             <v>0</v>
           </cell>
@@ -7997,14 +7796,6 @@
           <cell r="B256">
             <v>255</v>
           </cell>
-          <cell r="C256"/>
-          <cell r="D256"/>
-          <cell r="E256"/>
-          <cell r="F256"/>
-          <cell r="G256"/>
-          <cell r="H256"/>
-          <cell r="I256"/>
-          <cell r="J256"/>
           <cell r="K256">
             <v>0</v>
           </cell>
@@ -8013,14 +7804,6 @@
           <cell r="B257">
             <v>256</v>
           </cell>
-          <cell r="C257"/>
-          <cell r="D257"/>
-          <cell r="E257"/>
-          <cell r="F257"/>
-          <cell r="G257"/>
-          <cell r="H257"/>
-          <cell r="I257"/>
-          <cell r="J257"/>
           <cell r="K257">
             <v>0</v>
           </cell>
@@ -8029,14 +7812,6 @@
           <cell r="B258">
             <v>257</v>
           </cell>
-          <cell r="C258"/>
-          <cell r="D258"/>
-          <cell r="E258"/>
-          <cell r="F258"/>
-          <cell r="G258"/>
-          <cell r="H258"/>
-          <cell r="I258"/>
-          <cell r="J258"/>
           <cell r="K258">
             <v>0</v>
           </cell>
@@ -8045,14 +7820,6 @@
           <cell r="B259">
             <v>258</v>
           </cell>
-          <cell r="C259"/>
-          <cell r="D259"/>
-          <cell r="E259"/>
-          <cell r="F259"/>
-          <cell r="G259"/>
-          <cell r="H259"/>
-          <cell r="I259"/>
-          <cell r="J259"/>
           <cell r="K259">
             <v>0</v>
           </cell>
@@ -8061,14 +7828,6 @@
           <cell r="B260">
             <v>259</v>
           </cell>
-          <cell r="C260"/>
-          <cell r="D260"/>
-          <cell r="E260"/>
-          <cell r="F260"/>
-          <cell r="G260"/>
-          <cell r="H260"/>
-          <cell r="I260"/>
-          <cell r="J260"/>
           <cell r="K260">
             <v>0</v>
           </cell>
@@ -8077,14 +7836,6 @@
           <cell r="B261">
             <v>260</v>
           </cell>
-          <cell r="C261"/>
-          <cell r="D261"/>
-          <cell r="E261"/>
-          <cell r="F261"/>
-          <cell r="G261"/>
-          <cell r="H261"/>
-          <cell r="I261"/>
-          <cell r="J261"/>
           <cell r="K261">
             <v>0</v>
           </cell>
@@ -8093,14 +7844,6 @@
           <cell r="B262">
             <v>261</v>
           </cell>
-          <cell r="C262"/>
-          <cell r="D262"/>
-          <cell r="E262"/>
-          <cell r="F262"/>
-          <cell r="G262"/>
-          <cell r="H262"/>
-          <cell r="I262"/>
-          <cell r="J262"/>
           <cell r="K262">
             <v>0</v>
           </cell>
@@ -8109,14 +7852,6 @@
           <cell r="B263">
             <v>262</v>
           </cell>
-          <cell r="C263"/>
-          <cell r="D263"/>
-          <cell r="E263"/>
-          <cell r="F263"/>
-          <cell r="G263"/>
-          <cell r="H263"/>
-          <cell r="I263"/>
-          <cell r="J263"/>
           <cell r="K263">
             <v>0</v>
           </cell>
@@ -8125,14 +7860,6 @@
           <cell r="B264">
             <v>263</v>
           </cell>
-          <cell r="C264"/>
-          <cell r="D264"/>
-          <cell r="E264"/>
-          <cell r="F264"/>
-          <cell r="G264"/>
-          <cell r="H264"/>
-          <cell r="I264"/>
-          <cell r="J264"/>
           <cell r="K264">
             <v>0</v>
           </cell>
@@ -8141,14 +7868,6 @@
           <cell r="B265">
             <v>264</v>
           </cell>
-          <cell r="C265"/>
-          <cell r="D265"/>
-          <cell r="E265"/>
-          <cell r="F265"/>
-          <cell r="G265"/>
-          <cell r="H265"/>
-          <cell r="I265"/>
-          <cell r="J265"/>
           <cell r="K265">
             <v>0</v>
           </cell>
@@ -8157,14 +7876,6 @@
           <cell r="B266">
             <v>265</v>
           </cell>
-          <cell r="C266"/>
-          <cell r="D266"/>
-          <cell r="E266"/>
-          <cell r="F266"/>
-          <cell r="G266"/>
-          <cell r="H266"/>
-          <cell r="I266"/>
-          <cell r="J266"/>
           <cell r="K266">
             <v>0</v>
           </cell>
@@ -8173,14 +7884,6 @@
           <cell r="B267">
             <v>266</v>
           </cell>
-          <cell r="C267"/>
-          <cell r="D267"/>
-          <cell r="E267"/>
-          <cell r="F267"/>
-          <cell r="G267"/>
-          <cell r="H267"/>
-          <cell r="I267"/>
-          <cell r="J267"/>
           <cell r="K267">
             <v>0</v>
           </cell>
@@ -8189,14 +7892,6 @@
           <cell r="B268">
             <v>267</v>
           </cell>
-          <cell r="C268"/>
-          <cell r="D268"/>
-          <cell r="E268"/>
-          <cell r="F268"/>
-          <cell r="G268"/>
-          <cell r="H268"/>
-          <cell r="I268"/>
-          <cell r="J268"/>
           <cell r="K268">
             <v>0</v>
           </cell>
@@ -8205,14 +7900,6 @@
           <cell r="B269">
             <v>268</v>
           </cell>
-          <cell r="C269"/>
-          <cell r="D269"/>
-          <cell r="E269"/>
-          <cell r="F269"/>
-          <cell r="G269"/>
-          <cell r="H269"/>
-          <cell r="I269"/>
-          <cell r="J269"/>
           <cell r="K269">
             <v>0</v>
           </cell>
@@ -8221,14 +7908,6 @@
           <cell r="B270">
             <v>269</v>
           </cell>
-          <cell r="C270"/>
-          <cell r="D270"/>
-          <cell r="E270"/>
-          <cell r="F270"/>
-          <cell r="G270"/>
-          <cell r="H270"/>
-          <cell r="I270"/>
-          <cell r="J270"/>
           <cell r="K270">
             <v>0</v>
           </cell>
@@ -8237,14 +7916,6 @@
           <cell r="B271">
             <v>270</v>
           </cell>
-          <cell r="C271"/>
-          <cell r="D271"/>
-          <cell r="E271"/>
-          <cell r="F271"/>
-          <cell r="G271"/>
-          <cell r="H271"/>
-          <cell r="I271"/>
-          <cell r="J271"/>
           <cell r="K271">
             <v>0</v>
           </cell>
@@ -8253,14 +7924,6 @@
           <cell r="B272">
             <v>271</v>
           </cell>
-          <cell r="C272"/>
-          <cell r="D272"/>
-          <cell r="E272"/>
-          <cell r="F272"/>
-          <cell r="G272"/>
-          <cell r="H272"/>
-          <cell r="I272"/>
-          <cell r="J272"/>
           <cell r="K272">
             <v>0</v>
           </cell>
@@ -8269,14 +7932,6 @@
           <cell r="B273">
             <v>272</v>
           </cell>
-          <cell r="C273"/>
-          <cell r="D273"/>
-          <cell r="E273"/>
-          <cell r="F273"/>
-          <cell r="G273"/>
-          <cell r="H273"/>
-          <cell r="I273"/>
-          <cell r="J273"/>
           <cell r="K273">
             <v>0</v>
           </cell>
@@ -8285,14 +7940,6 @@
           <cell r="B274">
             <v>273</v>
           </cell>
-          <cell r="C274"/>
-          <cell r="D274"/>
-          <cell r="E274"/>
-          <cell r="F274"/>
-          <cell r="G274"/>
-          <cell r="H274"/>
-          <cell r="I274"/>
-          <cell r="J274"/>
           <cell r="K274">
             <v>0</v>
           </cell>
@@ -8301,14 +7948,6 @@
           <cell r="B275">
             <v>274</v>
           </cell>
-          <cell r="C275"/>
-          <cell r="D275"/>
-          <cell r="E275"/>
-          <cell r="F275"/>
-          <cell r="G275"/>
-          <cell r="H275"/>
-          <cell r="I275"/>
-          <cell r="J275"/>
           <cell r="K275">
             <v>0</v>
           </cell>
@@ -8317,14 +7956,6 @@
           <cell r="B276">
             <v>275</v>
           </cell>
-          <cell r="C276"/>
-          <cell r="D276"/>
-          <cell r="E276"/>
-          <cell r="F276"/>
-          <cell r="G276"/>
-          <cell r="H276"/>
-          <cell r="I276"/>
-          <cell r="J276"/>
           <cell r="K276">
             <v>0</v>
           </cell>
@@ -8333,14 +7964,6 @@
           <cell r="B277">
             <v>276</v>
           </cell>
-          <cell r="C277"/>
-          <cell r="D277"/>
-          <cell r="E277"/>
-          <cell r="F277"/>
-          <cell r="G277"/>
-          <cell r="H277"/>
-          <cell r="I277"/>
-          <cell r="J277"/>
           <cell r="K277">
             <v>0</v>
           </cell>
@@ -8349,14 +7972,6 @@
           <cell r="B278">
             <v>277</v>
           </cell>
-          <cell r="C278"/>
-          <cell r="D278"/>
-          <cell r="E278"/>
-          <cell r="F278"/>
-          <cell r="G278"/>
-          <cell r="H278"/>
-          <cell r="I278"/>
-          <cell r="J278"/>
           <cell r="K278">
             <v>0</v>
           </cell>
@@ -8365,14 +7980,6 @@
           <cell r="B279">
             <v>278</v>
           </cell>
-          <cell r="C279"/>
-          <cell r="D279"/>
-          <cell r="E279"/>
-          <cell r="F279"/>
-          <cell r="G279"/>
-          <cell r="H279"/>
-          <cell r="I279"/>
-          <cell r="J279"/>
           <cell r="K279">
             <v>0</v>
           </cell>
@@ -8381,14 +7988,6 @@
           <cell r="B280">
             <v>279</v>
           </cell>
-          <cell r="C280"/>
-          <cell r="D280"/>
-          <cell r="E280"/>
-          <cell r="F280"/>
-          <cell r="G280"/>
-          <cell r="H280"/>
-          <cell r="I280"/>
-          <cell r="J280"/>
           <cell r="K280">
             <v>0</v>
           </cell>
@@ -8397,14 +7996,6 @@
           <cell r="B281">
             <v>280</v>
           </cell>
-          <cell r="C281"/>
-          <cell r="D281"/>
-          <cell r="E281"/>
-          <cell r="F281"/>
-          <cell r="G281"/>
-          <cell r="H281"/>
-          <cell r="I281"/>
-          <cell r="J281"/>
           <cell r="K281">
             <v>0</v>
           </cell>
@@ -8413,14 +8004,6 @@
           <cell r="B282">
             <v>281</v>
           </cell>
-          <cell r="C282"/>
-          <cell r="D282"/>
-          <cell r="E282"/>
-          <cell r="F282"/>
-          <cell r="G282"/>
-          <cell r="H282"/>
-          <cell r="I282"/>
-          <cell r="J282"/>
           <cell r="K282">
             <v>0</v>
           </cell>
@@ -8429,14 +8012,6 @@
           <cell r="B283">
             <v>282</v>
           </cell>
-          <cell r="C283"/>
-          <cell r="D283"/>
-          <cell r="E283"/>
-          <cell r="F283"/>
-          <cell r="G283"/>
-          <cell r="H283"/>
-          <cell r="I283"/>
-          <cell r="J283"/>
           <cell r="K283">
             <v>0</v>
           </cell>
@@ -8445,14 +8020,6 @@
           <cell r="B284">
             <v>283</v>
           </cell>
-          <cell r="C284"/>
-          <cell r="D284"/>
-          <cell r="E284"/>
-          <cell r="F284"/>
-          <cell r="G284"/>
-          <cell r="H284"/>
-          <cell r="I284"/>
-          <cell r="J284"/>
           <cell r="K284">
             <v>0</v>
           </cell>
@@ -8461,14 +8028,6 @@
           <cell r="B285">
             <v>284</v>
           </cell>
-          <cell r="C285"/>
-          <cell r="D285"/>
-          <cell r="E285"/>
-          <cell r="F285"/>
-          <cell r="G285"/>
-          <cell r="H285"/>
-          <cell r="I285"/>
-          <cell r="J285"/>
           <cell r="K285">
             <v>0</v>
           </cell>
@@ -8477,14 +8036,6 @@
           <cell r="B286">
             <v>285</v>
           </cell>
-          <cell r="C286"/>
-          <cell r="D286"/>
-          <cell r="E286"/>
-          <cell r="F286"/>
-          <cell r="G286"/>
-          <cell r="H286"/>
-          <cell r="I286"/>
-          <cell r="J286"/>
           <cell r="K286">
             <v>0</v>
           </cell>
@@ -8493,14 +8044,6 @@
           <cell r="B287">
             <v>286</v>
           </cell>
-          <cell r="C287"/>
-          <cell r="D287"/>
-          <cell r="E287"/>
-          <cell r="F287"/>
-          <cell r="G287"/>
-          <cell r="H287"/>
-          <cell r="I287"/>
-          <cell r="J287"/>
           <cell r="K287">
             <v>0</v>
           </cell>
@@ -8509,14 +8052,6 @@
           <cell r="B288">
             <v>287</v>
           </cell>
-          <cell r="C288"/>
-          <cell r="D288"/>
-          <cell r="E288"/>
-          <cell r="F288"/>
-          <cell r="G288"/>
-          <cell r="H288"/>
-          <cell r="I288"/>
-          <cell r="J288"/>
           <cell r="K288">
             <v>0</v>
           </cell>
@@ -8525,14 +8060,6 @@
           <cell r="B289">
             <v>288</v>
           </cell>
-          <cell r="C289"/>
-          <cell r="D289"/>
-          <cell r="E289"/>
-          <cell r="F289"/>
-          <cell r="G289"/>
-          <cell r="H289"/>
-          <cell r="I289"/>
-          <cell r="J289"/>
           <cell r="K289">
             <v>0</v>
           </cell>
@@ -8541,14 +8068,6 @@
           <cell r="B290">
             <v>289</v>
           </cell>
-          <cell r="C290"/>
-          <cell r="D290"/>
-          <cell r="E290"/>
-          <cell r="F290"/>
-          <cell r="G290"/>
-          <cell r="H290"/>
-          <cell r="I290"/>
-          <cell r="J290"/>
           <cell r="K290">
             <v>0</v>
           </cell>
@@ -8557,14 +8076,6 @@
           <cell r="B291">
             <v>290</v>
           </cell>
-          <cell r="C291"/>
-          <cell r="D291"/>
-          <cell r="E291"/>
-          <cell r="F291"/>
-          <cell r="G291"/>
-          <cell r="H291"/>
-          <cell r="I291"/>
-          <cell r="J291"/>
           <cell r="K291">
             <v>0</v>
           </cell>
@@ -8573,14 +8084,6 @@
           <cell r="B292">
             <v>291</v>
           </cell>
-          <cell r="C292"/>
-          <cell r="D292"/>
-          <cell r="E292"/>
-          <cell r="F292"/>
-          <cell r="G292"/>
-          <cell r="H292"/>
-          <cell r="I292"/>
-          <cell r="J292"/>
           <cell r="K292">
             <v>0</v>
           </cell>
@@ -8589,14 +8092,6 @@
           <cell r="B293">
             <v>292</v>
           </cell>
-          <cell r="C293"/>
-          <cell r="D293"/>
-          <cell r="E293"/>
-          <cell r="F293"/>
-          <cell r="G293"/>
-          <cell r="H293"/>
-          <cell r="I293"/>
-          <cell r="J293"/>
           <cell r="K293">
             <v>0</v>
           </cell>
@@ -8605,14 +8100,6 @@
           <cell r="B294">
             <v>293</v>
           </cell>
-          <cell r="C294"/>
-          <cell r="D294"/>
-          <cell r="E294"/>
-          <cell r="F294"/>
-          <cell r="G294"/>
-          <cell r="H294"/>
-          <cell r="I294"/>
-          <cell r="J294"/>
           <cell r="K294">
             <v>0</v>
           </cell>
@@ -8621,14 +8108,6 @@
           <cell r="B295">
             <v>294</v>
           </cell>
-          <cell r="C295"/>
-          <cell r="D295"/>
-          <cell r="E295"/>
-          <cell r="F295"/>
-          <cell r="G295"/>
-          <cell r="H295"/>
-          <cell r="I295"/>
-          <cell r="J295"/>
           <cell r="K295">
             <v>0</v>
           </cell>
@@ -8637,14 +8116,6 @@
           <cell r="B296">
             <v>295</v>
           </cell>
-          <cell r="C296"/>
-          <cell r="D296"/>
-          <cell r="E296"/>
-          <cell r="F296"/>
-          <cell r="G296"/>
-          <cell r="H296"/>
-          <cell r="I296"/>
-          <cell r="J296"/>
           <cell r="K296">
             <v>0</v>
           </cell>
@@ -8653,14 +8124,6 @@
           <cell r="B297">
             <v>296</v>
           </cell>
-          <cell r="C297"/>
-          <cell r="D297"/>
-          <cell r="E297"/>
-          <cell r="F297"/>
-          <cell r="G297"/>
-          <cell r="H297"/>
-          <cell r="I297"/>
-          <cell r="J297"/>
           <cell r="K297">
             <v>0</v>
           </cell>
@@ -8669,14 +8132,6 @@
           <cell r="B298">
             <v>297</v>
           </cell>
-          <cell r="C298"/>
-          <cell r="D298"/>
-          <cell r="E298"/>
-          <cell r="F298"/>
-          <cell r="G298"/>
-          <cell r="H298"/>
-          <cell r="I298"/>
-          <cell r="J298"/>
           <cell r="K298">
             <v>0</v>
           </cell>
@@ -8685,14 +8140,6 @@
           <cell r="B299">
             <v>298</v>
           </cell>
-          <cell r="C299"/>
-          <cell r="D299"/>
-          <cell r="E299"/>
-          <cell r="F299"/>
-          <cell r="G299"/>
-          <cell r="H299"/>
-          <cell r="I299"/>
-          <cell r="J299"/>
           <cell r="K299">
             <v>0</v>
           </cell>
@@ -8701,14 +8148,6 @@
           <cell r="B300">
             <v>299</v>
           </cell>
-          <cell r="C300"/>
-          <cell r="D300"/>
-          <cell r="E300"/>
-          <cell r="F300"/>
-          <cell r="G300"/>
-          <cell r="H300"/>
-          <cell r="I300"/>
-          <cell r="J300"/>
           <cell r="K300">
             <v>0</v>
           </cell>
@@ -8717,14 +8156,6 @@
           <cell r="B301">
             <v>300</v>
           </cell>
-          <cell r="C301"/>
-          <cell r="D301"/>
-          <cell r="E301"/>
-          <cell r="F301"/>
-          <cell r="G301"/>
-          <cell r="H301"/>
-          <cell r="I301"/>
-          <cell r="J301"/>
           <cell r="K301">
             <v>0</v>
           </cell>
@@ -8733,14 +8164,6 @@
           <cell r="B302">
             <v>301</v>
           </cell>
-          <cell r="C302"/>
-          <cell r="D302"/>
-          <cell r="E302"/>
-          <cell r="F302"/>
-          <cell r="G302"/>
-          <cell r="H302"/>
-          <cell r="I302"/>
-          <cell r="J302"/>
           <cell r="K302">
             <v>0</v>
           </cell>
@@ -8749,14 +8172,6 @@
           <cell r="B303">
             <v>302</v>
           </cell>
-          <cell r="C303"/>
-          <cell r="D303"/>
-          <cell r="E303"/>
-          <cell r="F303"/>
-          <cell r="G303"/>
-          <cell r="H303"/>
-          <cell r="I303"/>
-          <cell r="J303"/>
           <cell r="K303">
             <v>0</v>
           </cell>
@@ -8765,14 +8180,6 @@
           <cell r="B304">
             <v>303</v>
           </cell>
-          <cell r="C304"/>
-          <cell r="D304"/>
-          <cell r="E304"/>
-          <cell r="F304"/>
-          <cell r="G304"/>
-          <cell r="H304"/>
-          <cell r="I304"/>
-          <cell r="J304"/>
           <cell r="K304">
             <v>0</v>
           </cell>
@@ -8781,14 +8188,6 @@
           <cell r="B305">
             <v>304</v>
           </cell>
-          <cell r="C305"/>
-          <cell r="D305"/>
-          <cell r="E305"/>
-          <cell r="F305"/>
-          <cell r="G305"/>
-          <cell r="H305"/>
-          <cell r="I305"/>
-          <cell r="J305"/>
           <cell r="K305">
             <v>0</v>
           </cell>
@@ -8797,14 +8196,6 @@
           <cell r="B306">
             <v>305</v>
           </cell>
-          <cell r="C306"/>
-          <cell r="D306"/>
-          <cell r="E306"/>
-          <cell r="F306"/>
-          <cell r="G306"/>
-          <cell r="H306"/>
-          <cell r="I306"/>
-          <cell r="J306"/>
           <cell r="K306">
             <v>0</v>
           </cell>
@@ -8813,14 +8204,6 @@
           <cell r="B307">
             <v>306</v>
           </cell>
-          <cell r="C307"/>
-          <cell r="D307"/>
-          <cell r="E307"/>
-          <cell r="F307"/>
-          <cell r="G307"/>
-          <cell r="H307"/>
-          <cell r="I307"/>
-          <cell r="J307"/>
           <cell r="K307">
             <v>0</v>
           </cell>
@@ -8829,14 +8212,6 @@
           <cell r="B308">
             <v>307</v>
           </cell>
-          <cell r="C308"/>
-          <cell r="D308"/>
-          <cell r="E308"/>
-          <cell r="F308"/>
-          <cell r="G308"/>
-          <cell r="H308"/>
-          <cell r="I308"/>
-          <cell r="J308"/>
           <cell r="K308">
             <v>0</v>
           </cell>
@@ -8845,14 +8220,6 @@
           <cell r="B309">
             <v>308</v>
           </cell>
-          <cell r="C309"/>
-          <cell r="D309"/>
-          <cell r="E309"/>
-          <cell r="F309"/>
-          <cell r="G309"/>
-          <cell r="H309"/>
-          <cell r="I309"/>
-          <cell r="J309"/>
           <cell r="K309">
             <v>0</v>
           </cell>
@@ -8861,14 +8228,6 @@
           <cell r="B310">
             <v>309</v>
           </cell>
-          <cell r="C310"/>
-          <cell r="D310"/>
-          <cell r="E310"/>
-          <cell r="F310"/>
-          <cell r="G310"/>
-          <cell r="H310"/>
-          <cell r="I310"/>
-          <cell r="J310"/>
           <cell r="K310">
             <v>0</v>
           </cell>
@@ -8877,14 +8236,6 @@
           <cell r="B311">
             <v>310</v>
           </cell>
-          <cell r="C311"/>
-          <cell r="D311"/>
-          <cell r="E311"/>
-          <cell r="F311"/>
-          <cell r="G311"/>
-          <cell r="H311"/>
-          <cell r="I311"/>
-          <cell r="J311"/>
           <cell r="K311">
             <v>0</v>
           </cell>
@@ -8893,14 +8244,6 @@
           <cell r="B312">
             <v>311</v>
           </cell>
-          <cell r="C312"/>
-          <cell r="D312"/>
-          <cell r="E312"/>
-          <cell r="F312"/>
-          <cell r="G312"/>
-          <cell r="H312"/>
-          <cell r="I312"/>
-          <cell r="J312"/>
           <cell r="K312">
             <v>0</v>
           </cell>
@@ -8909,14 +8252,6 @@
           <cell r="B313">
             <v>312</v>
           </cell>
-          <cell r="C313"/>
-          <cell r="D313"/>
-          <cell r="E313"/>
-          <cell r="F313"/>
-          <cell r="G313"/>
-          <cell r="H313"/>
-          <cell r="I313"/>
-          <cell r="J313"/>
           <cell r="K313">
             <v>0</v>
           </cell>
@@ -8925,14 +8260,6 @@
           <cell r="B314">
             <v>313</v>
           </cell>
-          <cell r="C314"/>
-          <cell r="D314"/>
-          <cell r="E314"/>
-          <cell r="F314"/>
-          <cell r="G314"/>
-          <cell r="H314"/>
-          <cell r="I314"/>
-          <cell r="J314"/>
           <cell r="K314">
             <v>0</v>
           </cell>
@@ -8941,14 +8268,6 @@
           <cell r="B315">
             <v>314</v>
           </cell>
-          <cell r="C315"/>
-          <cell r="D315"/>
-          <cell r="E315"/>
-          <cell r="F315"/>
-          <cell r="G315"/>
-          <cell r="H315"/>
-          <cell r="I315"/>
-          <cell r="J315"/>
           <cell r="K315">
             <v>0</v>
           </cell>
@@ -8957,14 +8276,6 @@
           <cell r="B316">
             <v>315</v>
           </cell>
-          <cell r="C316"/>
-          <cell r="D316"/>
-          <cell r="E316"/>
-          <cell r="F316"/>
-          <cell r="G316"/>
-          <cell r="H316"/>
-          <cell r="I316"/>
-          <cell r="J316"/>
           <cell r="K316">
             <v>0</v>
           </cell>
@@ -8973,14 +8284,6 @@
           <cell r="B317">
             <v>316</v>
           </cell>
-          <cell r="C317"/>
-          <cell r="D317"/>
-          <cell r="E317"/>
-          <cell r="F317"/>
-          <cell r="G317"/>
-          <cell r="H317"/>
-          <cell r="I317"/>
-          <cell r="J317"/>
           <cell r="K317">
             <v>0</v>
           </cell>
@@ -8989,14 +8292,6 @@
           <cell r="B318">
             <v>317</v>
           </cell>
-          <cell r="C318"/>
-          <cell r="D318"/>
-          <cell r="E318"/>
-          <cell r="F318"/>
-          <cell r="G318"/>
-          <cell r="H318"/>
-          <cell r="I318"/>
-          <cell r="J318"/>
           <cell r="K318">
             <v>0</v>
           </cell>
@@ -9005,14 +8300,6 @@
           <cell r="B319">
             <v>318</v>
           </cell>
-          <cell r="C319"/>
-          <cell r="D319"/>
-          <cell r="E319"/>
-          <cell r="F319"/>
-          <cell r="G319"/>
-          <cell r="H319"/>
-          <cell r="I319"/>
-          <cell r="J319"/>
           <cell r="K319">
             <v>0</v>
           </cell>
@@ -9021,14 +8308,6 @@
           <cell r="B320">
             <v>319</v>
           </cell>
-          <cell r="C320"/>
-          <cell r="D320"/>
-          <cell r="E320"/>
-          <cell r="F320"/>
-          <cell r="G320"/>
-          <cell r="H320"/>
-          <cell r="I320"/>
-          <cell r="J320"/>
           <cell r="K320">
             <v>0</v>
           </cell>
@@ -9037,14 +8316,6 @@
           <cell r="B321">
             <v>320</v>
           </cell>
-          <cell r="C321"/>
-          <cell r="D321"/>
-          <cell r="E321"/>
-          <cell r="F321"/>
-          <cell r="G321"/>
-          <cell r="H321"/>
-          <cell r="I321"/>
-          <cell r="J321"/>
           <cell r="K321">
             <v>0</v>
           </cell>
@@ -9053,14 +8324,6 @@
           <cell r="B322">
             <v>321</v>
           </cell>
-          <cell r="C322"/>
-          <cell r="D322"/>
-          <cell r="E322"/>
-          <cell r="F322"/>
-          <cell r="G322"/>
-          <cell r="H322"/>
-          <cell r="I322"/>
-          <cell r="J322"/>
           <cell r="K322">
             <v>0</v>
           </cell>
@@ -9069,14 +8332,6 @@
           <cell r="B323">
             <v>322</v>
           </cell>
-          <cell r="C323"/>
-          <cell r="D323"/>
-          <cell r="E323"/>
-          <cell r="F323"/>
-          <cell r="G323"/>
-          <cell r="H323"/>
-          <cell r="I323"/>
-          <cell r="J323"/>
           <cell r="K323">
             <v>0</v>
           </cell>
@@ -9085,14 +8340,6 @@
           <cell r="B324">
             <v>323</v>
           </cell>
-          <cell r="C324"/>
-          <cell r="D324"/>
-          <cell r="E324"/>
-          <cell r="F324"/>
-          <cell r="G324"/>
-          <cell r="H324"/>
-          <cell r="I324"/>
-          <cell r="J324"/>
           <cell r="K324">
             <v>0</v>
           </cell>
@@ -9101,14 +8348,6 @@
           <cell r="B325">
             <v>324</v>
           </cell>
-          <cell r="C325"/>
-          <cell r="D325"/>
-          <cell r="E325"/>
-          <cell r="F325"/>
-          <cell r="G325"/>
-          <cell r="H325"/>
-          <cell r="I325"/>
-          <cell r="J325"/>
           <cell r="K325">
             <v>0</v>
           </cell>
@@ -9117,14 +8356,6 @@
           <cell r="B326">
             <v>325</v>
           </cell>
-          <cell r="C326"/>
-          <cell r="D326"/>
-          <cell r="E326"/>
-          <cell r="F326"/>
-          <cell r="G326"/>
-          <cell r="H326"/>
-          <cell r="I326"/>
-          <cell r="J326"/>
           <cell r="K326">
             <v>0</v>
           </cell>
@@ -9133,14 +8364,6 @@
           <cell r="B327">
             <v>326</v>
           </cell>
-          <cell r="C327"/>
-          <cell r="D327"/>
-          <cell r="E327"/>
-          <cell r="F327"/>
-          <cell r="G327"/>
-          <cell r="H327"/>
-          <cell r="I327"/>
-          <cell r="J327"/>
           <cell r="K327">
             <v>0</v>
           </cell>
@@ -9149,14 +8372,6 @@
           <cell r="B328">
             <v>327</v>
           </cell>
-          <cell r="C328"/>
-          <cell r="D328"/>
-          <cell r="E328"/>
-          <cell r="F328"/>
-          <cell r="G328"/>
-          <cell r="H328"/>
-          <cell r="I328"/>
-          <cell r="J328"/>
           <cell r="K328">
             <v>0</v>
           </cell>
@@ -9165,14 +8380,6 @@
           <cell r="B329">
             <v>328</v>
           </cell>
-          <cell r="C329"/>
-          <cell r="D329"/>
-          <cell r="E329"/>
-          <cell r="F329"/>
-          <cell r="G329"/>
-          <cell r="H329"/>
-          <cell r="I329"/>
-          <cell r="J329"/>
           <cell r="K329">
             <v>0</v>
           </cell>
@@ -9181,14 +8388,6 @@
           <cell r="B330">
             <v>329</v>
           </cell>
-          <cell r="C330"/>
-          <cell r="D330"/>
-          <cell r="E330"/>
-          <cell r="F330"/>
-          <cell r="G330"/>
-          <cell r="H330"/>
-          <cell r="I330"/>
-          <cell r="J330"/>
           <cell r="K330">
             <v>0</v>
           </cell>
@@ -9197,14 +8396,6 @@
           <cell r="B331">
             <v>330</v>
           </cell>
-          <cell r="C331"/>
-          <cell r="D331"/>
-          <cell r="E331"/>
-          <cell r="F331"/>
-          <cell r="G331"/>
-          <cell r="H331"/>
-          <cell r="I331"/>
-          <cell r="J331"/>
           <cell r="K331">
             <v>0</v>
           </cell>
@@ -9213,14 +8404,6 @@
           <cell r="B332">
             <v>331</v>
           </cell>
-          <cell r="C332"/>
-          <cell r="D332"/>
-          <cell r="E332"/>
-          <cell r="F332"/>
-          <cell r="G332"/>
-          <cell r="H332"/>
-          <cell r="I332"/>
-          <cell r="J332"/>
           <cell r="K332">
             <v>0</v>
           </cell>
@@ -9229,14 +8412,6 @@
           <cell r="B333">
             <v>332</v>
           </cell>
-          <cell r="C333"/>
-          <cell r="D333"/>
-          <cell r="E333"/>
-          <cell r="F333"/>
-          <cell r="G333"/>
-          <cell r="H333"/>
-          <cell r="I333"/>
-          <cell r="J333"/>
           <cell r="K333">
             <v>0</v>
           </cell>
@@ -9245,14 +8420,6 @@
           <cell r="B334">
             <v>333</v>
           </cell>
-          <cell r="C334"/>
-          <cell r="D334"/>
-          <cell r="E334"/>
-          <cell r="F334"/>
-          <cell r="G334"/>
-          <cell r="H334"/>
-          <cell r="I334"/>
-          <cell r="J334"/>
           <cell r="K334">
             <v>0</v>
           </cell>
@@ -9261,14 +8428,6 @@
           <cell r="B335">
             <v>334</v>
           </cell>
-          <cell r="C335"/>
-          <cell r="D335"/>
-          <cell r="E335"/>
-          <cell r="F335"/>
-          <cell r="G335"/>
-          <cell r="H335"/>
-          <cell r="I335"/>
-          <cell r="J335"/>
           <cell r="K335">
             <v>0</v>
           </cell>
@@ -9277,14 +8436,6 @@
           <cell r="B336">
             <v>335</v>
           </cell>
-          <cell r="C336"/>
-          <cell r="D336"/>
-          <cell r="E336"/>
-          <cell r="F336"/>
-          <cell r="G336"/>
-          <cell r="H336"/>
-          <cell r="I336"/>
-          <cell r="J336"/>
           <cell r="K336">
             <v>0</v>
           </cell>
@@ -9293,14 +8444,6 @@
           <cell r="B337">
             <v>336</v>
           </cell>
-          <cell r="C337"/>
-          <cell r="D337"/>
-          <cell r="E337"/>
-          <cell r="F337"/>
-          <cell r="G337"/>
-          <cell r="H337"/>
-          <cell r="I337"/>
-          <cell r="J337"/>
           <cell r="K337">
             <v>0</v>
           </cell>
@@ -9309,14 +8452,6 @@
           <cell r="B338">
             <v>337</v>
           </cell>
-          <cell r="C338"/>
-          <cell r="D338"/>
-          <cell r="E338"/>
-          <cell r="F338"/>
-          <cell r="G338"/>
-          <cell r="H338"/>
-          <cell r="I338"/>
-          <cell r="J338"/>
           <cell r="K338">
             <v>0</v>
           </cell>
@@ -9325,14 +8460,6 @@
           <cell r="B339">
             <v>338</v>
           </cell>
-          <cell r="C339"/>
-          <cell r="D339"/>
-          <cell r="E339"/>
-          <cell r="F339"/>
-          <cell r="G339"/>
-          <cell r="H339"/>
-          <cell r="I339"/>
-          <cell r="J339"/>
           <cell r="K339">
             <v>0</v>
           </cell>
@@ -9341,14 +8468,6 @@
           <cell r="B340">
             <v>339</v>
           </cell>
-          <cell r="C340"/>
-          <cell r="D340"/>
-          <cell r="E340"/>
-          <cell r="F340"/>
-          <cell r="G340"/>
-          <cell r="H340"/>
-          <cell r="I340"/>
-          <cell r="J340"/>
           <cell r="K340">
             <v>0</v>
           </cell>
@@ -9357,14 +8476,6 @@
           <cell r="B341">
             <v>340</v>
           </cell>
-          <cell r="C341"/>
-          <cell r="D341"/>
-          <cell r="E341"/>
-          <cell r="F341"/>
-          <cell r="G341"/>
-          <cell r="H341"/>
-          <cell r="I341"/>
-          <cell r="J341"/>
           <cell r="K341">
             <v>0</v>
           </cell>
@@ -9373,14 +8484,6 @@
           <cell r="B342">
             <v>341</v>
           </cell>
-          <cell r="C342"/>
-          <cell r="D342"/>
-          <cell r="E342"/>
-          <cell r="F342"/>
-          <cell r="G342"/>
-          <cell r="H342"/>
-          <cell r="I342"/>
-          <cell r="J342"/>
           <cell r="K342">
             <v>0</v>
           </cell>
@@ -9389,14 +8492,6 @@
           <cell r="B343">
             <v>342</v>
           </cell>
-          <cell r="C343"/>
-          <cell r="D343"/>
-          <cell r="E343"/>
-          <cell r="F343"/>
-          <cell r="G343"/>
-          <cell r="H343"/>
-          <cell r="I343"/>
-          <cell r="J343"/>
           <cell r="K343">
             <v>0</v>
           </cell>
@@ -9405,14 +8500,6 @@
           <cell r="B344">
             <v>343</v>
           </cell>
-          <cell r="C344"/>
-          <cell r="D344"/>
-          <cell r="E344"/>
-          <cell r="F344"/>
-          <cell r="G344"/>
-          <cell r="H344"/>
-          <cell r="I344"/>
-          <cell r="J344"/>
           <cell r="K344">
             <v>0</v>
           </cell>
@@ -9421,14 +8508,6 @@
           <cell r="B345">
             <v>344</v>
           </cell>
-          <cell r="C345"/>
-          <cell r="D345"/>
-          <cell r="E345"/>
-          <cell r="F345"/>
-          <cell r="G345"/>
-          <cell r="H345"/>
-          <cell r="I345"/>
-          <cell r="J345"/>
           <cell r="K345">
             <v>0</v>
           </cell>
@@ -9437,14 +8516,6 @@
           <cell r="B346">
             <v>345</v>
           </cell>
-          <cell r="C346"/>
-          <cell r="D346"/>
-          <cell r="E346"/>
-          <cell r="F346"/>
-          <cell r="G346"/>
-          <cell r="H346"/>
-          <cell r="I346"/>
-          <cell r="J346"/>
           <cell r="K346">
             <v>0</v>
           </cell>
@@ -9453,14 +8524,6 @@
           <cell r="B347">
             <v>346</v>
           </cell>
-          <cell r="C347"/>
-          <cell r="D347"/>
-          <cell r="E347"/>
-          <cell r="F347"/>
-          <cell r="G347"/>
-          <cell r="H347"/>
-          <cell r="I347"/>
-          <cell r="J347"/>
           <cell r="K347">
             <v>0</v>
           </cell>
@@ -9469,14 +8532,6 @@
           <cell r="B348">
             <v>347</v>
           </cell>
-          <cell r="C348"/>
-          <cell r="D348"/>
-          <cell r="E348"/>
-          <cell r="F348"/>
-          <cell r="G348"/>
-          <cell r="H348"/>
-          <cell r="I348"/>
-          <cell r="J348"/>
           <cell r="K348">
             <v>0</v>
           </cell>
@@ -9485,14 +8540,6 @@
           <cell r="B349">
             <v>348</v>
           </cell>
-          <cell r="C349"/>
-          <cell r="D349"/>
-          <cell r="E349"/>
-          <cell r="F349"/>
-          <cell r="G349"/>
-          <cell r="H349"/>
-          <cell r="I349"/>
-          <cell r="J349"/>
           <cell r="K349">
             <v>0</v>
           </cell>
@@ -9501,14 +8548,6 @@
           <cell r="B350">
             <v>349</v>
           </cell>
-          <cell r="C350"/>
-          <cell r="D350"/>
-          <cell r="E350"/>
-          <cell r="F350"/>
-          <cell r="G350"/>
-          <cell r="H350"/>
-          <cell r="I350"/>
-          <cell r="J350"/>
           <cell r="K350">
             <v>0</v>
           </cell>
@@ -9517,14 +8556,6 @@
           <cell r="B351">
             <v>350</v>
           </cell>
-          <cell r="C351"/>
-          <cell r="D351"/>
-          <cell r="E351"/>
-          <cell r="F351"/>
-          <cell r="G351"/>
-          <cell r="H351"/>
-          <cell r="I351"/>
-          <cell r="J351"/>
           <cell r="K351">
             <v>0</v>
           </cell>
@@ -9533,14 +8564,6 @@
           <cell r="B352">
             <v>351</v>
           </cell>
-          <cell r="C352"/>
-          <cell r="D352"/>
-          <cell r="E352"/>
-          <cell r="F352"/>
-          <cell r="G352"/>
-          <cell r="H352"/>
-          <cell r="I352"/>
-          <cell r="J352"/>
           <cell r="K352">
             <v>0</v>
           </cell>
@@ -9549,14 +8572,6 @@
           <cell r="B353">
             <v>352</v>
           </cell>
-          <cell r="C353"/>
-          <cell r="D353"/>
-          <cell r="E353"/>
-          <cell r="F353"/>
-          <cell r="G353"/>
-          <cell r="H353"/>
-          <cell r="I353"/>
-          <cell r="J353"/>
           <cell r="K353">
             <v>0</v>
           </cell>
@@ -9565,14 +8580,6 @@
           <cell r="B354">
             <v>353</v>
           </cell>
-          <cell r="C354"/>
-          <cell r="D354"/>
-          <cell r="E354"/>
-          <cell r="F354"/>
-          <cell r="G354"/>
-          <cell r="H354"/>
-          <cell r="I354"/>
-          <cell r="J354"/>
           <cell r="K354">
             <v>0</v>
           </cell>
@@ -9581,14 +8588,6 @@
           <cell r="B355">
             <v>354</v>
           </cell>
-          <cell r="C355"/>
-          <cell r="D355"/>
-          <cell r="E355"/>
-          <cell r="F355"/>
-          <cell r="G355"/>
-          <cell r="H355"/>
-          <cell r="I355"/>
-          <cell r="J355"/>
           <cell r="K355">
             <v>0</v>
           </cell>
@@ -9597,14 +8596,6 @@
           <cell r="B356">
             <v>355</v>
           </cell>
-          <cell r="C356"/>
-          <cell r="D356"/>
-          <cell r="E356"/>
-          <cell r="F356"/>
-          <cell r="G356"/>
-          <cell r="H356"/>
-          <cell r="I356"/>
-          <cell r="J356"/>
           <cell r="K356">
             <v>0</v>
           </cell>
@@ -9613,14 +8604,6 @@
           <cell r="B357">
             <v>356</v>
           </cell>
-          <cell r="C357"/>
-          <cell r="D357"/>
-          <cell r="E357"/>
-          <cell r="F357"/>
-          <cell r="G357"/>
-          <cell r="H357"/>
-          <cell r="I357"/>
-          <cell r="J357"/>
           <cell r="K357">
             <v>0</v>
           </cell>
@@ -9629,14 +8612,6 @@
           <cell r="B358">
             <v>357</v>
           </cell>
-          <cell r="C358"/>
-          <cell r="D358"/>
-          <cell r="E358"/>
-          <cell r="F358"/>
-          <cell r="G358"/>
-          <cell r="H358"/>
-          <cell r="I358"/>
-          <cell r="J358"/>
           <cell r="K358">
             <v>0</v>
           </cell>
@@ -9645,14 +8620,6 @@
           <cell r="B359">
             <v>358</v>
           </cell>
-          <cell r="C359"/>
-          <cell r="D359"/>
-          <cell r="E359"/>
-          <cell r="F359"/>
-          <cell r="G359"/>
-          <cell r="H359"/>
-          <cell r="I359"/>
-          <cell r="J359"/>
           <cell r="K359">
             <v>0</v>
           </cell>
@@ -9661,14 +8628,6 @@
           <cell r="B360">
             <v>359</v>
           </cell>
-          <cell r="C360"/>
-          <cell r="D360"/>
-          <cell r="E360"/>
-          <cell r="F360"/>
-          <cell r="G360"/>
-          <cell r="H360"/>
-          <cell r="I360"/>
-          <cell r="J360"/>
           <cell r="K360">
             <v>0</v>
           </cell>
@@ -9677,14 +8636,6 @@
           <cell r="B361">
             <v>360</v>
           </cell>
-          <cell r="C361"/>
-          <cell r="D361"/>
-          <cell r="E361"/>
-          <cell r="F361"/>
-          <cell r="G361"/>
-          <cell r="H361"/>
-          <cell r="I361"/>
-          <cell r="J361"/>
           <cell r="K361">
             <v>0</v>
           </cell>
@@ -9693,14 +8644,6 @@
           <cell r="B362">
             <v>361</v>
           </cell>
-          <cell r="C362"/>
-          <cell r="D362"/>
-          <cell r="E362"/>
-          <cell r="F362"/>
-          <cell r="G362"/>
-          <cell r="H362"/>
-          <cell r="I362"/>
-          <cell r="J362"/>
           <cell r="K362">
             <v>0</v>
           </cell>
@@ -9709,14 +8652,6 @@
           <cell r="B363">
             <v>362</v>
           </cell>
-          <cell r="C363"/>
-          <cell r="D363"/>
-          <cell r="E363"/>
-          <cell r="F363"/>
-          <cell r="G363"/>
-          <cell r="H363"/>
-          <cell r="I363"/>
-          <cell r="J363"/>
           <cell r="K363">
             <v>0</v>
           </cell>
@@ -9725,14 +8660,6 @@
           <cell r="B364">
             <v>363</v>
           </cell>
-          <cell r="C364"/>
-          <cell r="D364"/>
-          <cell r="E364"/>
-          <cell r="F364"/>
-          <cell r="G364"/>
-          <cell r="H364"/>
-          <cell r="I364"/>
-          <cell r="J364"/>
           <cell r="K364">
             <v>0</v>
           </cell>
@@ -9741,14 +8668,6 @@
           <cell r="B365">
             <v>364</v>
           </cell>
-          <cell r="C365"/>
-          <cell r="D365"/>
-          <cell r="E365"/>
-          <cell r="F365"/>
-          <cell r="G365"/>
-          <cell r="H365"/>
-          <cell r="I365"/>
-          <cell r="J365"/>
           <cell r="K365">
             <v>0</v>
           </cell>
@@ -9757,14 +8676,6 @@
           <cell r="B366">
             <v>365</v>
           </cell>
-          <cell r="C366"/>
-          <cell r="D366"/>
-          <cell r="E366"/>
-          <cell r="F366"/>
-          <cell r="G366"/>
-          <cell r="H366"/>
-          <cell r="I366"/>
-          <cell r="J366"/>
           <cell r="K366">
             <v>0</v>
           </cell>
@@ -9773,14 +8684,6 @@
           <cell r="B367">
             <v>366</v>
           </cell>
-          <cell r="C367"/>
-          <cell r="D367"/>
-          <cell r="E367"/>
-          <cell r="F367"/>
-          <cell r="G367"/>
-          <cell r="H367"/>
-          <cell r="I367"/>
-          <cell r="J367"/>
           <cell r="K367">
             <v>0</v>
           </cell>
@@ -9789,14 +8692,6 @@
           <cell r="B368">
             <v>367</v>
           </cell>
-          <cell r="C368"/>
-          <cell r="D368"/>
-          <cell r="E368"/>
-          <cell r="F368"/>
-          <cell r="G368"/>
-          <cell r="H368"/>
-          <cell r="I368"/>
-          <cell r="J368"/>
           <cell r="K368">
             <v>0</v>
           </cell>
@@ -9805,14 +8700,6 @@
           <cell r="B369">
             <v>368</v>
           </cell>
-          <cell r="C369"/>
-          <cell r="D369"/>
-          <cell r="E369"/>
-          <cell r="F369"/>
-          <cell r="G369"/>
-          <cell r="H369"/>
-          <cell r="I369"/>
-          <cell r="J369"/>
           <cell r="K369">
             <v>0</v>
           </cell>
@@ -9821,14 +8708,6 @@
           <cell r="B370">
             <v>369</v>
           </cell>
-          <cell r="C370"/>
-          <cell r="D370"/>
-          <cell r="E370"/>
-          <cell r="F370"/>
-          <cell r="G370"/>
-          <cell r="H370"/>
-          <cell r="I370"/>
-          <cell r="J370"/>
           <cell r="K370">
             <v>0</v>
           </cell>
@@ -9837,14 +8716,6 @@
           <cell r="B371">
             <v>370</v>
           </cell>
-          <cell r="C371"/>
-          <cell r="D371"/>
-          <cell r="E371"/>
-          <cell r="F371"/>
-          <cell r="G371"/>
-          <cell r="H371"/>
-          <cell r="I371"/>
-          <cell r="J371"/>
           <cell r="K371">
             <v>0</v>
           </cell>
@@ -9853,14 +8724,6 @@
           <cell r="B372">
             <v>371</v>
           </cell>
-          <cell r="C372"/>
-          <cell r="D372"/>
-          <cell r="E372"/>
-          <cell r="F372"/>
-          <cell r="G372"/>
-          <cell r="H372"/>
-          <cell r="I372"/>
-          <cell r="J372"/>
           <cell r="K372">
             <v>0</v>
           </cell>
@@ -9869,14 +8732,6 @@
           <cell r="B373">
             <v>372</v>
           </cell>
-          <cell r="C373"/>
-          <cell r="D373"/>
-          <cell r="E373"/>
-          <cell r="F373"/>
-          <cell r="G373"/>
-          <cell r="H373"/>
-          <cell r="I373"/>
-          <cell r="J373"/>
           <cell r="K373">
             <v>0</v>
           </cell>
@@ -9885,14 +8740,6 @@
           <cell r="B374">
             <v>373</v>
           </cell>
-          <cell r="C374"/>
-          <cell r="D374"/>
-          <cell r="E374"/>
-          <cell r="F374"/>
-          <cell r="G374"/>
-          <cell r="H374"/>
-          <cell r="I374"/>
-          <cell r="J374"/>
           <cell r="K374">
             <v>0</v>
           </cell>
@@ -9901,14 +8748,6 @@
           <cell r="B375">
             <v>374</v>
           </cell>
-          <cell r="C375"/>
-          <cell r="D375"/>
-          <cell r="E375"/>
-          <cell r="F375"/>
-          <cell r="G375"/>
-          <cell r="H375"/>
-          <cell r="I375"/>
-          <cell r="J375"/>
           <cell r="K375">
             <v>0</v>
           </cell>
@@ -9917,14 +8756,6 @@
           <cell r="B376">
             <v>375</v>
           </cell>
-          <cell r="C376"/>
-          <cell r="D376"/>
-          <cell r="E376"/>
-          <cell r="F376"/>
-          <cell r="G376"/>
-          <cell r="H376"/>
-          <cell r="I376"/>
-          <cell r="J376"/>
           <cell r="K376">
             <v>0</v>
           </cell>
@@ -9933,14 +8764,6 @@
           <cell r="B377">
             <v>376</v>
           </cell>
-          <cell r="C377"/>
-          <cell r="D377"/>
-          <cell r="E377"/>
-          <cell r="F377"/>
-          <cell r="G377"/>
-          <cell r="H377"/>
-          <cell r="I377"/>
-          <cell r="J377"/>
           <cell r="K377">
             <v>0</v>
           </cell>
@@ -9949,14 +8772,6 @@
           <cell r="B378">
             <v>377</v>
           </cell>
-          <cell r="C378"/>
-          <cell r="D378"/>
-          <cell r="E378"/>
-          <cell r="F378"/>
-          <cell r="G378"/>
-          <cell r="H378"/>
-          <cell r="I378"/>
-          <cell r="J378"/>
           <cell r="K378">
             <v>0</v>
           </cell>
@@ -9965,14 +8780,6 @@
           <cell r="B379">
             <v>378</v>
           </cell>
-          <cell r="C379"/>
-          <cell r="D379"/>
-          <cell r="E379"/>
-          <cell r="F379"/>
-          <cell r="G379"/>
-          <cell r="H379"/>
-          <cell r="I379"/>
-          <cell r="J379"/>
           <cell r="K379">
             <v>0</v>
           </cell>
@@ -9981,14 +8788,6 @@
           <cell r="B380">
             <v>379</v>
           </cell>
-          <cell r="C380"/>
-          <cell r="D380"/>
-          <cell r="E380"/>
-          <cell r="F380"/>
-          <cell r="G380"/>
-          <cell r="H380"/>
-          <cell r="I380"/>
-          <cell r="J380"/>
           <cell r="K380">
             <v>0</v>
           </cell>
@@ -9997,14 +8796,6 @@
           <cell r="B381">
             <v>380</v>
           </cell>
-          <cell r="C381"/>
-          <cell r="D381"/>
-          <cell r="E381"/>
-          <cell r="F381"/>
-          <cell r="G381"/>
-          <cell r="H381"/>
-          <cell r="I381"/>
-          <cell r="J381"/>
           <cell r="K381">
             <v>0</v>
           </cell>
@@ -10013,14 +8804,6 @@
           <cell r="B382">
             <v>381</v>
           </cell>
-          <cell r="C382"/>
-          <cell r="D382"/>
-          <cell r="E382"/>
-          <cell r="F382"/>
-          <cell r="G382"/>
-          <cell r="H382"/>
-          <cell r="I382"/>
-          <cell r="J382"/>
           <cell r="K382">
             <v>0</v>
           </cell>
@@ -10029,14 +8812,6 @@
           <cell r="B383">
             <v>382</v>
           </cell>
-          <cell r="C383"/>
-          <cell r="D383"/>
-          <cell r="E383"/>
-          <cell r="F383"/>
-          <cell r="G383"/>
-          <cell r="H383"/>
-          <cell r="I383"/>
-          <cell r="J383"/>
           <cell r="K383">
             <v>0</v>
           </cell>
@@ -10045,14 +8820,6 @@
           <cell r="B384">
             <v>383</v>
           </cell>
-          <cell r="C384"/>
-          <cell r="D384"/>
-          <cell r="E384"/>
-          <cell r="F384"/>
-          <cell r="G384"/>
-          <cell r="H384"/>
-          <cell r="I384"/>
-          <cell r="J384"/>
           <cell r="K384">
             <v>0</v>
           </cell>
@@ -10061,14 +8828,6 @@
           <cell r="B385">
             <v>384</v>
           </cell>
-          <cell r="C385"/>
-          <cell r="D385"/>
-          <cell r="E385"/>
-          <cell r="F385"/>
-          <cell r="G385"/>
-          <cell r="H385"/>
-          <cell r="I385"/>
-          <cell r="J385"/>
           <cell r="K385">
             <v>0</v>
           </cell>
@@ -10077,14 +8836,6 @@
           <cell r="B386">
             <v>385</v>
           </cell>
-          <cell r="C386"/>
-          <cell r="D386"/>
-          <cell r="E386"/>
-          <cell r="F386"/>
-          <cell r="G386"/>
-          <cell r="H386"/>
-          <cell r="I386"/>
-          <cell r="J386"/>
           <cell r="K386">
             <v>0</v>
           </cell>
@@ -10093,14 +8844,6 @@
           <cell r="B387">
             <v>386</v>
           </cell>
-          <cell r="C387"/>
-          <cell r="D387"/>
-          <cell r="E387"/>
-          <cell r="F387"/>
-          <cell r="G387"/>
-          <cell r="H387"/>
-          <cell r="I387"/>
-          <cell r="J387"/>
           <cell r="K387">
             <v>0</v>
           </cell>
@@ -10109,14 +8852,6 @@
           <cell r="B388">
             <v>387</v>
           </cell>
-          <cell r="C388"/>
-          <cell r="D388"/>
-          <cell r="E388"/>
-          <cell r="F388"/>
-          <cell r="G388"/>
-          <cell r="H388"/>
-          <cell r="I388"/>
-          <cell r="J388"/>
           <cell r="K388">
             <v>0</v>
           </cell>
@@ -10125,14 +8860,6 @@
           <cell r="B389">
             <v>388</v>
           </cell>
-          <cell r="C389"/>
-          <cell r="D389"/>
-          <cell r="E389"/>
-          <cell r="F389"/>
-          <cell r="G389"/>
-          <cell r="H389"/>
-          <cell r="I389"/>
-          <cell r="J389"/>
           <cell r="K389">
             <v>0</v>
           </cell>
@@ -10141,14 +8868,6 @@
           <cell r="B390">
             <v>389</v>
           </cell>
-          <cell r="C390"/>
-          <cell r="D390"/>
-          <cell r="E390"/>
-          <cell r="F390"/>
-          <cell r="G390"/>
-          <cell r="H390"/>
-          <cell r="I390"/>
-          <cell r="J390"/>
           <cell r="K390">
             <v>0</v>
           </cell>
@@ -10157,14 +8876,6 @@
           <cell r="B391">
             <v>390</v>
           </cell>
-          <cell r="C391"/>
-          <cell r="D391"/>
-          <cell r="E391"/>
-          <cell r="F391"/>
-          <cell r="G391"/>
-          <cell r="H391"/>
-          <cell r="I391"/>
-          <cell r="J391"/>
           <cell r="K391">
             <v>0</v>
           </cell>
@@ -10173,14 +8884,6 @@
           <cell r="B392">
             <v>391</v>
           </cell>
-          <cell r="C392"/>
-          <cell r="D392"/>
-          <cell r="E392"/>
-          <cell r="F392"/>
-          <cell r="G392"/>
-          <cell r="H392"/>
-          <cell r="I392"/>
-          <cell r="J392"/>
           <cell r="K392">
             <v>0</v>
           </cell>
@@ -10189,14 +8892,6 @@
           <cell r="B393">
             <v>392</v>
           </cell>
-          <cell r="C393"/>
-          <cell r="D393"/>
-          <cell r="E393"/>
-          <cell r="F393"/>
-          <cell r="G393"/>
-          <cell r="H393"/>
-          <cell r="I393"/>
-          <cell r="J393"/>
           <cell r="K393">
             <v>0</v>
           </cell>
@@ -10205,14 +8900,6 @@
           <cell r="B394">
             <v>393</v>
           </cell>
-          <cell r="C394"/>
-          <cell r="D394"/>
-          <cell r="E394"/>
-          <cell r="F394"/>
-          <cell r="G394"/>
-          <cell r="H394"/>
-          <cell r="I394"/>
-          <cell r="J394"/>
           <cell r="K394">
             <v>0</v>
           </cell>
@@ -10221,14 +8908,6 @@
           <cell r="B395">
             <v>394</v>
           </cell>
-          <cell r="C395"/>
-          <cell r="D395"/>
-          <cell r="E395"/>
-          <cell r="F395"/>
-          <cell r="G395"/>
-          <cell r="H395"/>
-          <cell r="I395"/>
-          <cell r="J395"/>
           <cell r="K395">
             <v>0</v>
           </cell>
@@ -10237,14 +8916,6 @@
           <cell r="B396">
             <v>395</v>
           </cell>
-          <cell r="C396"/>
-          <cell r="D396"/>
-          <cell r="E396"/>
-          <cell r="F396"/>
-          <cell r="G396"/>
-          <cell r="H396"/>
-          <cell r="I396"/>
-          <cell r="J396"/>
           <cell r="K396">
             <v>0</v>
           </cell>
@@ -10253,14 +8924,6 @@
           <cell r="B397">
             <v>396</v>
           </cell>
-          <cell r="C397"/>
-          <cell r="D397"/>
-          <cell r="E397"/>
-          <cell r="F397"/>
-          <cell r="G397"/>
-          <cell r="H397"/>
-          <cell r="I397"/>
-          <cell r="J397"/>
           <cell r="K397">
             <v>0</v>
           </cell>
@@ -10269,14 +8932,6 @@
           <cell r="B398">
             <v>397</v>
           </cell>
-          <cell r="C398"/>
-          <cell r="D398"/>
-          <cell r="E398"/>
-          <cell r="F398"/>
-          <cell r="G398"/>
-          <cell r="H398"/>
-          <cell r="I398"/>
-          <cell r="J398"/>
           <cell r="K398">
             <v>0</v>
           </cell>
@@ -25345,7 +24000,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5527B6-58FD-524E-85CF-A53FB2DF16C9}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -25810,6 +24465,9 @@
       <c r="E14" s="1">
         <v>0.66666999999999998</v>
       </c>
+      <c r="F14" s="1">
+        <v>1600</v>
+      </c>
       <c r="G14" s="1" t="s">
         <v>413</v>
       </c>
@@ -25833,6 +24491,9 @@
       <c r="E15" s="1">
         <v>0.5</v>
       </c>
+      <c r="F15" s="1">
+        <v>5000</v>
+      </c>
       <c r="G15" s="1" t="s">
         <v>413</v>
       </c>
@@ -25856,6 +24517,9 @@
       <c r="E16" s="1">
         <v>1.143</v>
       </c>
+      <c r="F16" s="1">
+        <v>3500</v>
+      </c>
       <c r="G16" s="1" t="s">
         <v>413</v>
       </c>
@@ -25879,6 +24543,9 @@
       <c r="E17" s="1">
         <v>1.3340000000000001</v>
       </c>
+      <c r="F17" s="1">
+        <v>4000</v>
+      </c>
       <c r="G17" s="1" t="s">
         <v>413</v>
       </c>
@@ -25910,6 +24577,58 @@
       </c>
       <c r="H18" s="1" t="s">
         <v>477</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D19" s="1">
+        <v>5000</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5000</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <v>6500</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F20" s="1">
+        <v>6500</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319BE1CE-F320-5942-AAAD-A37260D59DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C233E1-62D8-B247-A7E1-C97ACBC6AE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="21500" windowHeight="19940" activeTab="2" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>

--- a/WebsiteData.xlsx
+++ b/WebsiteData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jkevans/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA39605-251A-1C42-838F-371EA75BAD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827F12A8-D481-9248-A70D-F74F164E04FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="840" windowWidth="11040" windowHeight="19940" activeTab="3" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="18700" windowHeight="19940" activeTab="3" xr2:uid="{C762ECBC-EE1A-4249-820F-B10BC232F997}"/>
   </bookViews>
   <sheets>
     <sheet name="Projections" sheetId="1" r:id="rId1"/>
@@ -10128,7 +10128,7 @@
             <v>Veteran, returning starters, big man edge, elite coach, poor shooting, elite rebounding</v>
           </cell>
           <cell r="D2">
-            <v>2.7069999999999999</v>
+            <v>2.5</v>
           </cell>
           <cell r="E2">
             <v>3.9</v>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="E2" s="1">
         <f>VLOOKUP($A2,[2]TeamRtg!$A$2:$E$366,4,FALSE)</f>
-        <v>2.7069999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP($A2,[2]TeamRtg!$A$2:$E$366,5,FALSE)</f>
